--- a/untranslated/downloads/data-excel/8.8.1.xlsx
+++ b/untranslated/downloads/data-excel/8.8.1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="12645" windowHeight="10605"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12135"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="48">
   <si>
     <t>Кыргызская Республика</t>
   </si>
@@ -167,7 +167,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -275,6 +275,12 @@
       <name val="Times New Roman CE"/>
       <charset val="204"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Times New Roman CE"/>
+      <charset val="204"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -328,7 +334,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
@@ -408,15 +414,6 @@
     <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -434,6 +431,41 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -746,7 +778,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:T68"/>
+  <dimension ref="A1:U70"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="3" width="38" style="3" customWidth="1"/>
@@ -756,7 +788,7 @@
     <col min="16" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="6" customFormat="1" ht="48" customHeight="1">
+    <row r="1" spans="1:21" s="6" customFormat="1" ht="48" customHeight="1">
       <c r="A1" s="8" t="s">
         <v>43</v>
       </c>
@@ -778,7 +810,7 @@
       <c r="M1" s="5"/>
       <c r="N1" s="5"/>
     </row>
-    <row r="2" spans="1:20" ht="22.5">
+    <row r="2" spans="1:21" ht="22.5">
       <c r="A2" s="26" t="s">
         <v>47</v>
       </c>
@@ -800,7 +832,7 @@
       <c r="M2" s="1"/>
       <c r="N2" s="1"/>
     </row>
-    <row r="3" spans="1:20" ht="15.75" thickBot="1">
+    <row r="3" spans="1:21" ht="15.75" thickBot="1">
       <c r="B3" s="16"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
@@ -813,15 +845,16 @@
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
-    </row>
-    <row r="4" spans="1:20" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A4" s="34" t="s">
+      <c r="U3"/>
+    </row>
+    <row r="4" spans="1:21" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A4" s="41" t="s">
         <v>38</v>
       </c>
-      <c r="B4" s="34" t="s">
+      <c r="B4" s="41" t="s">
         <v>37</v>
       </c>
-      <c r="C4" s="34" t="s">
+      <c r="C4" s="41" t="s">
         <v>10</v>
       </c>
       <c r="D4" s="9" t="s">
@@ -843,11 +876,12 @@
       <c r="R4" s="9"/>
       <c r="S4" s="9"/>
       <c r="T4" s="9"/>
-    </row>
-    <row r="5" spans="1:20" ht="15.75" thickBot="1">
-      <c r="A5" s="35"/>
-      <c r="B5" s="35"/>
-      <c r="C5" s="35"/>
+      <c r="U4" s="43"/>
+    </row>
+    <row r="5" spans="1:21" ht="15.75" thickBot="1">
+      <c r="A5" s="42"/>
+      <c r="B5" s="42"/>
+      <c r="C5" s="42"/>
       <c r="D5" s="12">
         <v>2007</v>
       </c>
@@ -899,8 +933,11 @@
       <c r="T5" s="12">
         <v>2023</v>
       </c>
-    </row>
-    <row r="6" spans="1:20" s="18" customFormat="1">
+      <c r="U5" s="44">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" s="18" customFormat="1">
       <c r="A6" s="19" t="s">
         <v>11</v>
       </c>
@@ -961,8 +998,11 @@
       <c r="T6" s="17">
         <v>21.053924363776723</v>
       </c>
-    </row>
-    <row r="7" spans="1:20">
+      <c r="U6" s="45">
+        <v>20.609912487140825</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21">
       <c r="A7" s="4" t="s">
         <v>34</v>
       </c>
@@ -1023,8 +1063,11 @@
       <c r="T7" s="14">
         <v>9.963239083382005</v>
       </c>
-    </row>
-    <row r="8" spans="1:20">
+      <c r="U7" s="46">
+        <v>7.1440168858580932</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21">
       <c r="A8" s="4" t="s">
         <v>31</v>
       </c>
@@ -1085,8 +1128,11 @@
       <c r="T8" s="14">
         <v>28.68463041646498</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" s="2" customFormat="1">
+      <c r="U8" s="46">
+        <v>29.260254564214708</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" s="2" customFormat="1">
       <c r="A9" s="22" t="s">
         <v>13</v>
       </c>
@@ -1147,8 +1193,11 @@
       <c r="T9" s="14">
         <v>5.5380184969817794</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" customFormat="1">
+      <c r="U9" s="45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" customFormat="1">
       <c r="A10" s="4" t="s">
         <v>34</v>
       </c>
@@ -1195,8 +1244,11 @@
       <c r="T10" s="14" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" customFormat="1">
+      <c r="U10" s="46" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" customFormat="1">
       <c r="A11" s="4" t="s">
         <v>31</v>
       </c>
@@ -1257,8 +1309,11 @@
       <c r="T11" s="14">
         <v>12.785271367384771</v>
       </c>
-    </row>
-    <row r="12" spans="1:20" s="2" customFormat="1" ht="12.75" customHeight="1">
+      <c r="U11" s="46" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" s="2" customFormat="1" ht="12.75" customHeight="1">
       <c r="A12" s="22" t="s">
         <v>15</v>
       </c>
@@ -1319,8 +1374,11 @@
       <c r="T12" s="14">
         <v>27.411597597747264</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" customFormat="1">
+      <c r="U12" s="45">
+        <v>39.737491721355894</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" customFormat="1">
       <c r="A13" s="4" t="s">
         <v>34</v>
       </c>
@@ -1381,8 +1439,11 @@
       <c r="T13" s="14">
         <v>2.1979954281695093</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" customFormat="1">
+      <c r="U13" s="46">
+        <v>2.1249920312798829</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" customFormat="1">
       <c r="A14" s="4" t="s">
         <v>31</v>
       </c>
@@ -1443,8 +1504,11 @@
       <c r="T14" s="14">
         <v>60.410793395086586</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" s="2" customFormat="1">
+      <c r="U14" s="46">
+        <v>88.923470238426063</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" s="2" customFormat="1">
       <c r="A15" s="22" t="s">
         <v>16</v>
       </c>
@@ -1505,8 +1569,11 @@
       <c r="T15" s="14">
         <v>21.576524741081702</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" customFormat="1">
+      <c r="U15" s="45">
+        <v>24.687091120053328</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" customFormat="1">
       <c r="A16" s="4" t="s">
         <v>34</v>
       </c>
@@ -1565,8 +1632,11 @@
       <c r="T16" s="14">
         <v>4.3817369205152925</v>
       </c>
-    </row>
-    <row r="17" spans="1:20" customFormat="1">
+      <c r="U16" s="46">
+        <v>13.932104212139508</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" customFormat="1">
       <c r="A17" s="4" t="s">
         <v>31</v>
       </c>
@@ -1627,8 +1697,11 @@
       <c r="T17" s="14">
         <v>42.350449973530964</v>
       </c>
-    </row>
-    <row r="18" spans="1:20" s="2" customFormat="1">
+      <c r="U17" s="46">
+        <v>36.892589859808155</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" s="2" customFormat="1">
       <c r="A18" s="22" t="s">
         <v>17</v>
       </c>
@@ -1689,8 +1762,11 @@
       <c r="T18" s="14">
         <v>3.9264959949740854</v>
       </c>
-    </row>
-    <row r="19" spans="1:20" customFormat="1">
+      <c r="U18" s="45">
+        <v>18.840907378099327</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" customFormat="1">
       <c r="A19" s="4" t="s">
         <v>34</v>
       </c>
@@ -1751,8 +1827,11 @@
       <c r="T19" s="14" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="20" spans="1:20" customFormat="1">
+      <c r="U19" s="46">
+        <v>6.6286623359406072</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" customFormat="1">
       <c r="A20" s="4" t="s">
         <v>31</v>
       </c>
@@ -1813,8 +1892,11 @@
       <c r="T20" s="14">
         <v>9.4020308386611511</v>
       </c>
-    </row>
-    <row r="21" spans="1:20" s="2" customFormat="1">
+      <c r="U20" s="46">
+        <v>34.928396786587491</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" s="2" customFormat="1">
       <c r="A21" s="22" t="s">
         <v>19</v>
       </c>
@@ -1875,8 +1957,11 @@
       <c r="T21" s="14" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="22" spans="1:20" customFormat="1">
+      <c r="U21" s="45" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" customFormat="1">
       <c r="A22" s="4" t="s">
         <v>34</v>
       </c>
@@ -1937,8 +2022,11 @@
       <c r="T22" s="14" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="23" spans="1:20" customFormat="1">
+      <c r="U22" s="45" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" customFormat="1">
       <c r="A23" s="4" t="s">
         <v>31</v>
       </c>
@@ -1999,8 +2087,11 @@
       <c r="T23" s="14" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="24" spans="1:20" s="2" customFormat="1">
+      <c r="U23" s="45" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" s="2" customFormat="1">
       <c r="A24" s="22" t="s">
         <v>21</v>
       </c>
@@ -2061,8 +2152,11 @@
       <c r="T24" s="14" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="25" spans="1:20" customFormat="1">
+      <c r="U24" s="45">
+        <v>8.6937622256031304</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" customFormat="1">
       <c r="A25" s="4" t="s">
         <v>34</v>
       </c>
@@ -2123,8 +2217,11 @@
       <c r="T25" s="14" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="26" spans="1:20" customFormat="1">
+      <c r="U25" s="46">
+        <v>7.9636855936927615</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21" customFormat="1">
       <c r="A26" s="4" t="s">
         <v>31</v>
       </c>
@@ -2185,8 +2282,11 @@
       <c r="T26" s="14" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="27" spans="1:20" s="2" customFormat="1">
+      <c r="U26" s="46">
+        <v>9.5712098009188367</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21" s="2" customFormat="1">
       <c r="A27" s="22" t="s">
         <v>23</v>
       </c>
@@ -2247,8 +2347,11 @@
       <c r="T27" s="14">
         <v>18.390381830302751</v>
       </c>
-    </row>
-    <row r="28" spans="1:20" customFormat="1">
+      <c r="U27" s="45">
+        <v>7.2294818268900576</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" customFormat="1">
       <c r="A28" s="4" t="s">
         <v>34</v>
       </c>
@@ -2309,8 +2412,11 @@
       <c r="T28" s="14">
         <v>13.767941348569854</v>
       </c>
-    </row>
-    <row r="29" spans="1:20" customFormat="1">
+      <c r="U28" s="46" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21" customFormat="1">
       <c r="A29" s="4" t="s">
         <v>31</v>
       </c>
@@ -2371,8 +2477,11 @@
       <c r="T29" s="14">
         <v>20.707863811282333</v>
       </c>
-    </row>
-    <row r="30" spans="1:20" s="2" customFormat="1">
+      <c r="U29" s="46">
+        <v>14.255167498218105</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21" s="2" customFormat="1">
       <c r="A30" s="22" t="s">
         <v>25</v>
       </c>
@@ -2433,8 +2542,11 @@
       <c r="T30" s="14">
         <v>32.401828145251145</v>
       </c>
-    </row>
-    <row r="31" spans="1:20" customFormat="1">
+      <c r="U30" s="45">
+        <v>21.91149793114694</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" customFormat="1">
       <c r="A31" s="4" t="s">
         <v>34</v>
       </c>
@@ -2495,8 +2607,11 @@
       <c r="T31" s="14">
         <v>26.276104738838367</v>
       </c>
-    </row>
-    <row r="32" spans="1:20" customFormat="1">
+      <c r="U31" s="46">
+        <v>16.391931071929843</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21" customFormat="1">
       <c r="A32" s="4" t="s">
         <v>31</v>
       </c>
@@ -2557,8 +2672,11 @@
       <c r="T32" s="14">
         <v>38.468501086169439</v>
       </c>
-    </row>
-    <row r="33" spans="1:20" s="2" customFormat="1">
+      <c r="U32" s="46">
+        <v>27.373650326963045</v>
+      </c>
+    </row>
+    <row r="33" spans="1:21" s="2" customFormat="1">
       <c r="A33" s="22" t="s">
         <v>27</v>
       </c>
@@ -2619,8 +2737,11 @@
       <c r="T33" s="14">
         <v>4.7916816406717935</v>
       </c>
-    </row>
-    <row r="34" spans="1:20" customFormat="1">
+      <c r="U33" s="45">
+        <v>2.2536226984878192</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21" customFormat="1">
       <c r="A34" s="4" t="s">
         <v>34</v>
       </c>
@@ -2681,8 +2802,11 @@
       <c r="T34" s="14" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="35" spans="1:20" customFormat="1" ht="15.75" thickBot="1">
+      <c r="U34" s="46" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="35" spans="1:21" customFormat="1" ht="15.75" thickBot="1">
       <c r="A35" s="7" t="s">
         <v>31</v>
       </c>
@@ -2743,100 +2867,108 @@
       <c r="T35" s="15">
         <v>10.173974972021568</v>
       </c>
-    </row>
-    <row r="36" spans="1:20" ht="15.75" thickBot="1">
+      <c r="U35" s="15">
+        <v>4.9541738915035918</v>
+      </c>
+    </row>
+    <row r="36" spans="1:21" ht="15.75" thickBot="1">
       <c r="Q36" s="27"/>
       <c r="R36" s="28"/>
       <c r="S36" s="28"/>
-      <c r="T36" s="38"/>
-    </row>
-    <row r="37" spans="1:20" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A37" s="34" t="s">
+      <c r="T36" s="35"/>
+      <c r="U36" s="35"/>
+    </row>
+    <row r="37" spans="1:21" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A37" s="41" t="s">
         <v>38</v>
       </c>
-      <c r="B37" s="34" t="s">
+      <c r="B37" s="41" t="s">
         <v>37</v>
       </c>
-      <c r="C37" s="34" t="s">
+      <c r="C37" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="D37" s="33" t="s">
+      <c r="D37" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="E37" s="33"/>
-      <c r="F37" s="33"/>
-      <c r="G37" s="33"/>
-      <c r="H37" s="33"/>
-      <c r="I37" s="33"/>
-      <c r="J37" s="33"/>
-      <c r="K37" s="33"/>
-      <c r="L37" s="33"/>
-      <c r="M37" s="33"/>
-      <c r="N37" s="33"/>
-      <c r="O37" s="33"/>
-      <c r="P37" s="33"/>
-      <c r="Q37" s="36"/>
-      <c r="R37" s="36"/>
-      <c r="S37" s="36"/>
-      <c r="T37" s="39"/>
-    </row>
-    <row r="38" spans="1:20" s="2" customFormat="1" ht="15" customHeight="1" thickBot="1">
-      <c r="A38" s="35"/>
-      <c r="B38" s="35"/>
-      <c r="C38" s="35"/>
-      <c r="D38" s="37">
+      <c r="E37" s="40"/>
+      <c r="F37" s="40"/>
+      <c r="G37" s="40"/>
+      <c r="H37" s="40"/>
+      <c r="I37" s="40"/>
+      <c r="J37" s="40"/>
+      <c r="K37" s="40"/>
+      <c r="L37" s="40"/>
+      <c r="M37" s="40"/>
+      <c r="N37" s="40"/>
+      <c r="O37" s="40"/>
+      <c r="P37" s="40"/>
+      <c r="Q37" s="33"/>
+      <c r="R37" s="33"/>
+      <c r="S37" s="33"/>
+      <c r="T37" s="36"/>
+      <c r="U37" s="47"/>
+    </row>
+    <row r="38" spans="1:21" s="2" customFormat="1" ht="15" customHeight="1" thickBot="1">
+      <c r="A38" s="42"/>
+      <c r="B38" s="42"/>
+      <c r="C38" s="42"/>
+      <c r="D38" s="34">
         <v>2007</v>
       </c>
-      <c r="E38" s="37">
+      <c r="E38" s="34">
         <v>2008</v>
       </c>
-      <c r="F38" s="37">
+      <c r="F38" s="34">
         <v>2009</v>
       </c>
-      <c r="G38" s="37">
+      <c r="G38" s="34">
         <v>2010</v>
       </c>
-      <c r="H38" s="37">
+      <c r="H38" s="34">
         <v>2011</v>
       </c>
-      <c r="I38" s="37">
+      <c r="I38" s="34">
         <v>2012</v>
       </c>
-      <c r="J38" s="37">
+      <c r="J38" s="34">
         <v>2013</v>
       </c>
-      <c r="K38" s="37">
+      <c r="K38" s="34">
         <v>2014</v>
       </c>
-      <c r="L38" s="37">
+      <c r="L38" s="34">
         <v>2015</v>
       </c>
-      <c r="M38" s="37">
+      <c r="M38" s="34">
         <v>2016</v>
       </c>
-      <c r="N38" s="37">
+      <c r="N38" s="34">
         <v>2017</v>
       </c>
-      <c r="O38" s="37">
+      <c r="O38" s="34">
         <v>2018</v>
       </c>
-      <c r="P38" s="37">
+      <c r="P38" s="34">
         <v>2019</v>
       </c>
-      <c r="Q38" s="37">
+      <c r="Q38" s="34">
         <v>2020</v>
       </c>
-      <c r="R38" s="37">
+      <c r="R38" s="34">
         <v>2021</v>
       </c>
-      <c r="S38" s="37">
+      <c r="S38" s="34">
         <v>2022</v>
       </c>
-      <c r="T38" s="40">
+      <c r="T38" s="37">
         <v>2023</v>
       </c>
-    </row>
-    <row r="39" spans="1:20" s="2" customFormat="1">
+      <c r="U38" s="48">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="39" spans="1:21" s="2" customFormat="1">
       <c r="A39" s="19" t="s">
         <v>11</v>
       </c>
@@ -2894,11 +3026,14 @@
       <c r="S39" s="29">
         <v>11.2</v>
       </c>
-      <c r="T39" s="41">
+      <c r="T39" s="38">
         <v>1.9</v>
       </c>
-    </row>
-    <row r="40" spans="1:20" s="2" customFormat="1">
+      <c r="U39" s="49">
+        <v>3.3469088654331252</v>
+      </c>
+    </row>
+    <row r="40" spans="1:21" s="2" customFormat="1">
       <c r="A40" s="4" t="s">
         <v>34</v>
       </c>
@@ -2956,11 +3091,14 @@
       <c r="S40" s="30">
         <v>0.3</v>
       </c>
-      <c r="T40" s="42" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="41" spans="1:20">
+      <c r="T40" s="39" t="s">
+        <v>41</v>
+      </c>
+      <c r="U40" s="50" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="41" spans="1:21">
       <c r="A41" s="4" t="s">
         <v>31</v>
       </c>
@@ -3021,8 +3159,11 @@
       <c r="T41" s="32">
         <v>3.9</v>
       </c>
-    </row>
-    <row r="42" spans="1:20">
+      <c r="U41" s="50">
+        <v>7.3150636410536771</v>
+      </c>
+    </row>
+    <row r="42" spans="1:21">
       <c r="A42" s="22" t="s">
         <v>13</v>
       </c>
@@ -3083,8 +3224,11 @@
       <c r="T42" s="32" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="43" spans="1:20">
+      <c r="U42" s="51">
+        <v>5.3975279322070486</v>
+      </c>
+    </row>
+    <row r="43" spans="1:21">
       <c r="A43" s="4" t="s">
         <v>34</v>
       </c>
@@ -3145,8 +3289,11 @@
       <c r="T43" s="14" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="44" spans="1:20">
+      <c r="U43" s="46" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="44" spans="1:21">
       <c r="A44" s="4" t="s">
         <v>31</v>
       </c>
@@ -3207,8 +3354,11 @@
       <c r="T44" s="32" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="45" spans="1:20">
+      <c r="U44" s="50">
+        <v>12.884107453456162</v>
+      </c>
+    </row>
+    <row r="45" spans="1:21">
       <c r="A45" s="22" t="s">
         <v>15</v>
       </c>
@@ -3269,8 +3419,11 @@
       <c r="T45" s="32">
         <v>1.2</v>
       </c>
-    </row>
-    <row r="46" spans="1:20">
+      <c r="U45" s="51">
+        <v>6.0208320789933172</v>
+      </c>
+    </row>
+    <row r="46" spans="1:21">
       <c r="A46" s="4" t="s">
         <v>34</v>
       </c>
@@ -3331,8 +3484,11 @@
       <c r="T46" s="14" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="47" spans="1:20">
+      <c r="U46" s="46" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="47" spans="1:21">
       <c r="A47" s="4" t="s">
         <v>31</v>
       </c>
@@ -3393,8 +3549,11 @@
       <c r="T47" s="32">
         <v>2.9</v>
       </c>
-    </row>
-    <row r="48" spans="1:20">
+      <c r="U47" s="50">
+        <v>13.89429222475407</v>
+      </c>
+    </row>
+    <row r="48" spans="1:21">
       <c r="A48" s="22" t="s">
         <v>16</v>
       </c>
@@ -3453,8 +3612,11 @@
       <c r="T48" s="32">
         <v>2.4</v>
       </c>
-    </row>
-    <row r="49" spans="1:20">
+      <c r="U48" s="51">
+        <v>4.9374182240106652</v>
+      </c>
+    </row>
+    <row r="49" spans="1:21">
       <c r="A49" s="4" t="s">
         <v>34</v>
       </c>
@@ -3515,8 +3677,11 @@
       <c r="T49" s="14" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="50" spans="1:20">
+      <c r="U49" s="46" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="50" spans="1:21">
       <c r="A50" s="4" t="s">
         <v>31</v>
       </c>
@@ -3577,8 +3742,11 @@
       <c r="T50" s="32">
         <v>5.3</v>
       </c>
-    </row>
-    <row r="51" spans="1:20">
+      <c r="U50" s="50">
+        <v>10.540739959945189</v>
+      </c>
+    </row>
+    <row r="51" spans="1:21">
       <c r="A51" s="22" t="s">
         <v>17</v>
       </c>
@@ -3639,8 +3807,11 @@
       <c r="T51" s="32">
         <v>3.9</v>
       </c>
-    </row>
-    <row r="52" spans="1:20">
+      <c r="U51" s="51">
+        <v>3.7681814756198659</v>
+      </c>
+    </row>
+    <row r="52" spans="1:21">
       <c r="A52" s="4" t="s">
         <v>34</v>
       </c>
@@ -3701,8 +3872,11 @@
       <c r="T52" s="14" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="53" spans="1:20">
+      <c r="U52" s="46" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="53" spans="1:21">
       <c r="A53" s="4" t="s">
         <v>31</v>
       </c>
@@ -3763,8 +3937,11 @@
       <c r="T53" s="32">
         <v>9.4</v>
       </c>
-    </row>
-    <row r="54" spans="1:20">
+      <c r="U53" s="50">
+        <v>8.7320991966468728</v>
+      </c>
+    </row>
+    <row r="54" spans="1:21">
       <c r="A54" s="22" t="s">
         <v>19</v>
       </c>
@@ -3825,8 +4002,11 @@
       <c r="T54" s="32" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="55" spans="1:20">
+      <c r="U54" s="51" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="55" spans="1:21">
       <c r="A55" s="4" t="s">
         <v>34</v>
       </c>
@@ -3887,8 +4067,11 @@
       <c r="T55" s="14" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="56" spans="1:20">
+      <c r="U55" s="46" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="56" spans="1:21">
       <c r="A56" s="4" t="s">
         <v>31</v>
       </c>
@@ -3949,8 +4132,11 @@
       <c r="T56" s="32" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="57" spans="1:20">
+      <c r="U56" s="50" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="57" spans="1:21">
       <c r="A57" s="22" t="s">
         <v>21</v>
       </c>
@@ -4011,8 +4197,11 @@
       <c r="T57" s="32">
         <v>4.5999999999999996</v>
       </c>
-    </row>
-    <row r="58" spans="1:20">
+      <c r="U57" s="50" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="58" spans="1:21">
       <c r="A58" s="4" t="s">
         <v>34</v>
       </c>
@@ -4073,8 +4262,11 @@
       <c r="T58" s="32" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="59" spans="1:20">
+      <c r="U58" s="50" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="59" spans="1:21">
       <c r="A59" s="4" t="s">
         <v>31</v>
       </c>
@@ -4135,8 +4327,11 @@
       <c r="T59" s="32">
         <v>9.9</v>
       </c>
-    </row>
-    <row r="60" spans="1:20">
+      <c r="U59" s="50" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="60" spans="1:21">
       <c r="A60" s="22" t="s">
         <v>23</v>
       </c>
@@ -4197,8 +4392,11 @@
       <c r="T60" s="32">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="61" spans="1:20">
+      <c r="U60" s="51">
+        <v>5.422111370167543</v>
+      </c>
+    </row>
+    <row r="61" spans="1:21">
       <c r="A61" s="4" t="s">
         <v>34</v>
       </c>
@@ -4259,8 +4457,11 @@
       <c r="T61" s="32" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="62" spans="1:20">
+      <c r="U61" s="50" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="62" spans="1:21">
       <c r="A62" s="4" t="s">
         <v>31</v>
       </c>
@@ -4321,8 +4522,11 @@
       <c r="T62" s="32">
         <v>1.7</v>
       </c>
-    </row>
-    <row r="63" spans="1:20">
+      <c r="U62" s="50">
+        <v>10.691375623663578</v>
+      </c>
+    </row>
+    <row r="63" spans="1:21">
       <c r="A63" s="22" t="s">
         <v>25</v>
       </c>
@@ -4383,8 +4587,11 @@
       <c r="T63" s="32">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="64" spans="1:20">
+      <c r="U63" s="51">
+        <v>2.0382788773159941</v>
+      </c>
+    </row>
+    <row r="64" spans="1:21">
       <c r="A64" s="4" t="s">
         <v>34</v>
       </c>
@@ -4445,8 +4652,11 @@
       <c r="T64" s="14" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="65" spans="1:20">
+      <c r="U64" s="46" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="65" spans="1:21">
       <c r="A65" s="4" t="s">
         <v>31</v>
       </c>
@@ -4507,8 +4717,11 @@
       <c r="T65" s="32">
         <v>2.2999999999999998</v>
       </c>
-    </row>
-    <row r="66" spans="1:20">
+      <c r="U65" s="50">
+        <v>4.0553556039945251</v>
+      </c>
+    </row>
+    <row r="66" spans="1:21">
       <c r="A66" s="22" t="s">
         <v>27</v>
       </c>
@@ -4569,8 +4782,11 @@
       <c r="T66" s="32">
         <v>9.6</v>
       </c>
-    </row>
-    <row r="67" spans="1:20">
+      <c r="U66" s="51">
+        <v>4.5072453969756383</v>
+      </c>
+    </row>
+    <row r="67" spans="1:21">
       <c r="A67" s="4" t="s">
         <v>34</v>
       </c>
@@ -4631,8 +4847,11 @@
       <c r="T67" s="14" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="68" spans="1:20" ht="15.75" thickBot="1">
+      <c r="U67" s="46" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="68" spans="1:21" ht="15.75" thickBot="1">
       <c r="A68" s="7" t="s">
         <v>31</v>
       </c>
@@ -4693,6 +4912,12 @@
       <c r="T68" s="13">
         <v>20.3</v>
       </c>
+      <c r="U68" s="52">
+        <v>9.9083477830071836</v>
+      </c>
+    </row>
+    <row r="70" spans="1:21">
+      <c r="U70"/>
     </row>
   </sheetData>
   <mergeCells count="7">
